--- a/data/trending_integrated_20261006_09.xlsx
+++ b/data/trending_integrated_20261006_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44000</v>
+        <v>48400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+8.78%</t>
+          <t>'+19.65%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
-        <v>744</v>
+        <v>907</v>
       </c>
       <c r="H2" t="n">
         <v>14.1</v>
@@ -601,7 +601,7 @@
         <v>42700</v>
       </c>
       <c r="L2" t="n">
-        <v>44200</v>
+        <v>49400</v>
       </c>
       <c r="M2" t="n">
         <v>42150</v>
@@ -610,7 +610,7 @@
         <v>14.11</v>
       </c>
       <c r="O2" t="n">
-        <v>11182025000</v>
+        <v>63353399600</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성에 대한 AI 분석 결과 및 커뮤니티 내 긍정적 분위기 형성. 관련 공지 및 결과 확인에 대한 언급.</t>
+          <t>FDA 승인 기대감과 AI 분석 기반의 긍정적 전망. 공시나 공식 발표는 아직 확인되지 않음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1826000</v>
+        <v>21800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.81%</t>
+          <t>'+16.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>252</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>1010</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>49.76</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1841000</v>
+        <v>18790</v>
       </c>
       <c r="K3" t="n">
-        <v>1835000</v>
+        <v>21400</v>
       </c>
       <c r="L3" t="n">
-        <v>1837000</v>
+        <v>22300</v>
       </c>
       <c r="M3" t="n">
-        <v>1823000</v>
+        <v>21000</v>
       </c>
       <c r="N3" t="n">
-        <v>49.77</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>231519573500</v>
+        <v>58680077690</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>30550</v>
       </c>
       <c r="Q3" t="n">
-        <v>403000</v>
+        <v>6100</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,27 +718,211 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 신고가 및 엔비디아 강세에 따른 SK하이닉스의 상승 기대감이 있으나, 단기 하락 전망도 존재. 메모리 반도체 업황 개선에 대한 언급.</t>
+          <t>미국 보안주 강세 및 AI 해킹 사태 관련 보안주 투자 심리 고조. 실제 실적 근거는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['보안주', 'AI', '해킹']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>276000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+0.00%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>329</v>
+      </c>
+      <c r="F4" t="n">
+        <v>223</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>276000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>278500</v>
+      </c>
+      <c r="L4" t="n">
+        <v>279000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>275500</v>
+      </c>
+      <c r="N4" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="O4" t="n">
+        <v>382927109750</v>
+      </c>
+      <c r="P4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>반도체 시장 랠리에 따른 30만 돌파 기대감. 일부 뉴스와 개인적 전망에 기반함.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['반도체', '영업이익', '외국인']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1819000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-1.20%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>301</v>
+      </c>
+      <c r="F5" t="n">
+        <v>209</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1074</v>
+      </c>
+      <c r="H5" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1813000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O5" t="n">
+        <v>512100135000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>미국 증시 신고가 및 엔비디아 강세에 따른 SK하이닉스의 상승 기대감이 있으나, 단기 하락 전망도 존재. 메모리 반도체 업황 개선에 대한 언급.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
         <v>0.2</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>['엔비디아', '반도체', 'AI']</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="X5" t="n">
         <v>6</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_09.xlsx
+++ b/data/trending_integrated_20261006_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48400</v>
+        <v>48550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.65%</t>
+          <t>'+20.02%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="G2" t="n">
-        <v>907</v>
+        <v>1104</v>
       </c>
       <c r="H2" t="n">
         <v>14.1</v>
@@ -601,7 +601,7 @@
         <v>42700</v>
       </c>
       <c r="L2" t="n">
-        <v>49400</v>
+        <v>49600</v>
       </c>
       <c r="M2" t="n">
         <v>42150</v>
@@ -610,7 +610,7 @@
         <v>14.11</v>
       </c>
       <c r="O2" t="n">
-        <v>63353399600</v>
+        <v>97442329125</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -619,23 +619,23 @@
         <v>24150</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>468000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감과 AI 분석 기반의 긍정적 전망. 공시나 공식 발표는 아직 확인되지 않음.</t>
+          <t>HLB의 간암 신약 미국 FDA 승인 임박 가능성에 대한 기대감 고조. AI 분석 결과 및 공식 블로그 정보 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', 'AI', '승인']</t>
+          <t>['FDA 승인', '간암 신약', 'AI 분석']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21800</v>
+        <v>20900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.02%</t>
+          <t>'+11.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
@@ -696,13 +696,13 @@
         <v>22300</v>
       </c>
       <c r="M3" t="n">
-        <v>21000</v>
+        <v>20750</v>
       </c>
       <c r="N3" t="n">
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>58680077690</v>
+        <v>83679340415</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -711,23 +711,23 @@
         <v>6100</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 및 AI 해킹 사태 관련 보안주 투자 심리 고조. 실제 실적 근거는 부족.</t>
+          <t>미국 보안주 최고가 경신에 따른 엑스게이트의 동반 상승 기대. AI 해킹 사태로 인한 보안주 전반의 관심 증대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '해킹']</t>
+          <t>['보안주', 'AI 해킹', '상승 기대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>276000</v>
+        <v>277000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>329</v>
+        <v>385</v>
       </c>
       <c r="F4" t="n">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="G4" t="n">
-        <v>1744</v>
+        <v>1872</v>
       </c>
       <c r="H4" t="n">
         <v>46.41</v>
@@ -788,13 +788,13 @@
         <v>279000</v>
       </c>
       <c r="M4" t="n">
-        <v>275500</v>
+        <v>275000</v>
       </c>
       <c r="N4" t="n">
         <v>46.41</v>
       </c>
       <c r="O4" t="n">
-        <v>382927109750</v>
+        <v>518889311500</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -803,7 +803,7 @@
         <v>90200</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-338000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -854,13 +854,13 @@
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="F5" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="G5" t="n">
-        <v>1074</v>
+        <v>1117</v>
       </c>
       <c r="H5" t="n">
         <v>49.76</v>
@@ -880,13 +880,13 @@
         <v>1837000</v>
       </c>
       <c r="M5" t="n">
-        <v>1813000</v>
+        <v>1810000</v>
       </c>
       <c r="N5" t="n">
         <v>49.77</v>
       </c>
       <c r="O5" t="n">
-        <v>512100135000</v>
+        <v>713991191500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,7 +895,7 @@
         <v>403000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-120000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261006_09.xlsx
+++ b/data/trending_integrated_20261006_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48550</v>
+        <v>50700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.02%</t>
+          <t>'+25.34%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="F2" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="G2" t="n">
-        <v>1104</v>
+        <v>1275</v>
       </c>
       <c r="H2" t="n">
         <v>14.1</v>
@@ -601,7 +601,7 @@
         <v>42700</v>
       </c>
       <c r="L2" t="n">
-        <v>49600</v>
+        <v>50700</v>
       </c>
       <c r="M2" t="n">
         <v>42150</v>
@@ -610,7 +610,7 @@
         <v>14.11</v>
       </c>
       <c r="O2" t="n">
-        <v>97442329125</v>
+        <v>128107235000</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB의 간암 신약 미국 FDA 승인 임박 가능성에 대한 기대감 고조. AI 분석 결과 및 공식 블로그 정보 언급.</t>
+          <t>HLB 간암 신약 미국 FDA 승인 임박 및 VAI 등장으로 인한 급등 기대감 형성. 공시 기반 결과 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'AI 분석']</t>
+          <t>['FDA 승인', '신약', 'VAI']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20900</v>
+        <v>20650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.23%</t>
+          <t>'+9.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
@@ -696,13 +696,13 @@
         <v>22300</v>
       </c>
       <c r="M3" t="n">
-        <v>20750</v>
+        <v>20500</v>
       </c>
       <c r="N3" t="n">
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>83679340415</v>
+        <v>93280496115</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 최고가 경신에 따른 엑스게이트의 동반 상승 기대. AI 해킹 사태로 인한 보안주 전반의 관심 증대.</t>
+          <t>대통령 지시로 인한 보안주 부각 및 AI 해킹 사태로 엑스게이트 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>277000</v>
+        <v>18670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+4.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>385</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>254</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>1872</v>
+        <v>257</v>
       </c>
       <c r="H4" t="n">
-        <v>46.41</v>
+        <v>3.81</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>276000</v>
+        <v>17800</v>
       </c>
       <c r="K4" t="n">
-        <v>278500</v>
+        <v>18040</v>
       </c>
       <c r="L4" t="n">
-        <v>279000</v>
+        <v>18880</v>
       </c>
       <c r="M4" t="n">
-        <v>275000</v>
+        <v>17950</v>
       </c>
       <c r="N4" t="n">
-        <v>46.41</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>518889311500</v>
+        <v>121041476375</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>-338000</v>
+        <v>454000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 시장 랠리에 따른 30만 돌파 기대감. 일부 뉴스와 개인적 전망에 기반함.</t>
+          <t>미국 광통신 섹터 강세에 따른 대한광통신 매수 기회 포착. 매물 소화 및 상승 흐름 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '영업이익', '외국인']</t>
+          <t>['광통신', '섹터', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1819000</v>
+        <v>278000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'+0.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="F5" t="n">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="G5" t="n">
-        <v>1117</v>
+        <v>1921</v>
       </c>
       <c r="H5" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K5" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L5" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M5" t="n">
-        <v>1810000</v>
+        <v>275000</v>
       </c>
       <c r="N5" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O5" t="n">
-        <v>713991191500</v>
+        <v>654225294250</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R5" t="n">
-        <v>-120000</v>
+        <v>-338000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 신고가 및 엔비디아 강세에 따른 SK하이닉스의 상승 기대감이 있으나, 단기 하락 전망도 존재. 메모리 반도체 업황 개선에 대한 언급.</t>
+          <t>반도체 시장 랠리에 따른 30만 돌파 기대감. 일부 뉴스와 개인적 전망에 기반함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', 'AI']</t>
+          <t>['반도체', '영업이익', '외국인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -923,6 +923,98 @@
         </is>
       </c>
       <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1821000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-1.09%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>383</v>
+      </c>
+      <c r="F6" t="n">
+        <v>256</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1160</v>
+      </c>
+      <c r="H6" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1810000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O6" t="n">
+        <v>832589388500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>미국 증시 신고가 및 엔비디아 강세에 따른 SK하이닉스의 상승 기대감이 있으나, 단기 하락 전망도 존재. 메모리 반도체 업황 개선에 대한 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['엔비디아', '반도체', 'AI']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261006_09.xlsx
+++ b/data/trending_integrated_20261006_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50700</v>
+        <v>47200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.34%</t>
+          <t>'+16.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
-        <v>1275</v>
+        <v>1519</v>
       </c>
       <c r="H2" t="n">
         <v>14.1</v>
@@ -610,7 +610,7 @@
         <v>14.11</v>
       </c>
       <c r="O2" t="n">
-        <v>128107235000</v>
+        <v>162004206650</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 미국 FDA 승인 임박 및 VAI 등장으로 인한 급등 기대감 형성. 공시 기반 결과 확인.</t>
+          <t>HLB 간암 신약의 미국 FDA 승인 임박에 대한 기대감 고조. AI 답변 및 FDA 문서 근거 제시, 공시 블로그 결과 언급. 승인 시 대폭 상승 및 100만원 목표가 제시. 허위 사실 유포에 대한 법적 대응 시사.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 승인', '신약', 'VAI']</t>
+          <t>['FDA 승인', '간암 신약', 'AI 답변']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20650</v>
+        <v>20600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.90%</t>
+          <t>'+9.63%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.21</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
@@ -696,13 +696,13 @@
         <v>22300</v>
       </c>
       <c r="M3" t="n">
-        <v>20500</v>
+        <v>20450</v>
       </c>
       <c r="N3" t="n">
         <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>93280496115</v>
+        <v>99164843415</v>
       </c>
       <c r="P3" t="n">
         <v>30550</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대통령 지시로 인한 보안주 부각 및 AI 해킹 사태로 엑스게이트 추가 상승 기대.</t>
+          <t>대통령 보안 점검 지시에 따른 보안주 부각 및 엑스게이트 금융 고객사 보유 언급. 은행 보안 위협 및 타 보안주(안랩) 상승에 따른 동반 상승 기대감 존재. 단기 급등 및 갭 상승 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', 'AI 해킹', '상승 기대']</t>
+          <t>['보안주', '금융 고객사', '동반 상승']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18670</v>
+        <v>18500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.89%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="H4" t="n">
         <v>3.81</v>
@@ -794,7 +794,7 @@
         <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>121041476375</v>
+        <v>129345090595</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 대한광통신 매수 기회 포착. 매물 소화 및 상승 흐름 기대.</t>
+          <t>미국 증시에서 광통신 섹터 강세 및 대한광통신 대장주 언급. 매수 기회 및 매물 소화 의견 존재하나, 상승 흐름에 대한 불안감 및 특정 시간대 매수 주의 의견도 나타남.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '섹터', '매물 소화']</t>
+          <t>['광통신', '대장주', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="F5" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G5" t="n">
-        <v>1921</v>
+        <v>1959</v>
       </c>
       <c r="H5" t="n">
         <v>46.41</v>
@@ -886,7 +886,7 @@
         <v>46.41</v>
       </c>
       <c r="O5" t="n">
-        <v>654225294250</v>
+        <v>744388816750</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1821000</v>
+        <v>1819000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'-1.20%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="F6" t="n">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="G6" t="n">
-        <v>1160</v>
+        <v>1231</v>
       </c>
       <c r="H6" t="n">
         <v>49.76</v>
@@ -978,7 +978,7 @@
         <v>49.77</v>
       </c>
       <c r="O6" t="n">
-        <v>832589388500</v>
+        <v>944760577500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>

--- a/data/trending_integrated_20261006_09.xlsx
+++ b/data/trending_integrated_20261006_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47200</v>
+        <v>13010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.69%</t>
+          <t>'+29.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>1519</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40450</v>
+        <v>10010</v>
       </c>
       <c r="K2" t="n">
-        <v>42700</v>
+        <v>10530</v>
       </c>
       <c r="L2" t="n">
-        <v>50700</v>
+        <v>13010</v>
       </c>
       <c r="M2" t="n">
-        <v>42150</v>
+        <v>10110</v>
       </c>
       <c r="N2" t="n">
-        <v>14.11</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>162004206650</v>
+        <v>46707194400</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>22250</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>6000</v>
       </c>
       <c r="R2" t="n">
-        <v>468000</v>
+        <v>310000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HLB 간암 신약의 미국 FDA 승인 임박에 대한 기대감 고조. AI 답변 및 FDA 문서 근거 제시, 공시 블로그 결과 언급. 승인 시 대폭 상승 및 100만원 목표가 제시. 허위 사실 유포에 대한 법적 대응 시사.</t>
+          <t>기타법인 대규모 자사주 매집 확인 및 유증 물량 소화 완료 기대감. VAI 관련 기술 기대감 반영.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'AI 답변']</t>
+          <t>['자사주 매집', '유증 물량', 'VAI']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20600</v>
+        <v>48050</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.63%</t>
+          <t>'+18.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>401</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>270</v>
       </c>
       <c r="G3" t="n">
-        <v>130</v>
+        <v>1721</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>14.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18790</v>
+        <v>40450</v>
       </c>
       <c r="K3" t="n">
-        <v>21400</v>
+        <v>42700</v>
       </c>
       <c r="L3" t="n">
-        <v>22300</v>
+        <v>50700</v>
       </c>
       <c r="M3" t="n">
-        <v>20450</v>
+        <v>42150</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>99164843415</v>
+        <v>177825796625</v>
       </c>
       <c r="P3" t="n">
-        <v>30550</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>6100</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>468000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대통령 보안 점검 지시에 따른 보안주 부각 및 엑스게이트 금융 고객사 보유 언급. 은행 보안 위협 및 타 보안주(안랩) 상승에 따른 동반 상승 기대감 존재. 단기 급등 및 갭 상승 예상.</t>
+          <t>FDA 승인 임박 가능성 및 VAI 기술 관련 긍정적 정보 확산. 항암 신약 기대감에 따른 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '금융 고객사', '동반 상승']</t>
+          <t>['FDA 승인', 'VAI', '간암 신약']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18500</v>
+        <v>20300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.93%</t>
+          <t>'+8.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="E4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F4" t="n">
         <v>49</v>
       </c>
-      <c r="F4" t="n">
-        <v>39</v>
-      </c>
       <c r="G4" t="n">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>3.81</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17800</v>
+        <v>18790</v>
       </c>
       <c r="K4" t="n">
-        <v>18040</v>
+        <v>21400</v>
       </c>
       <c r="L4" t="n">
-        <v>18880</v>
+        <v>22300</v>
       </c>
       <c r="M4" t="n">
-        <v>17950</v>
+        <v>20250</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>129345090595</v>
+        <v>102593258415</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>30550</v>
       </c>
       <c r="Q4" t="n">
-        <v>1272</v>
+        <v>6100</v>
       </c>
       <c r="R4" t="n">
-        <v>454000</v>
+        <v>36000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시에서 광통신 섹터 강세 및 대한광통신 대장주 언급. 매수 기회 및 매물 소화 의견 존재하나, 상승 흐름에 대한 불안감 및 특정 시간대 매수 주의 의견도 나타남.</t>
+          <t>국가 안보 중요성 부각 및 금융기관 보안 위협에 따른 보안주 투자 심리 개선 기대. 샌즈랩, 안랩 등 경쟁사 동반 강세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광통신', '대장주', '매물 소화']</t>
+          <t>['보안주', '금융 고객사', '국가 안보']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>278000</v>
+        <v>18590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.72%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>419</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>270</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>1959</v>
+        <v>321</v>
       </c>
       <c r="H5" t="n">
-        <v>46.41</v>
+        <v>3.81</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>276000</v>
+        <v>17800</v>
       </c>
       <c r="K5" t="n">
-        <v>278500</v>
+        <v>18040</v>
       </c>
       <c r="L5" t="n">
-        <v>279000</v>
+        <v>18880</v>
       </c>
       <c r="M5" t="n">
-        <v>275000</v>
+        <v>17950</v>
       </c>
       <c r="N5" t="n">
-        <v>46.41</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>744388816750</v>
+        <v>143390016640</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>-338000</v>
+        <v>454000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 시장 랠리에 따른 30만 돌파 기대감. 일부 뉴스와 개인적 전망에 기반함.</t>
+          <t>미국 광통신 섹터 강세와 프로그램 매수세 유입에 따른 상승 기대감. 다만, 특정 시간대 매수 주의 의견 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '영업이익', '외국인']</t>
+          <t>['광통신', '프로그램 매수', '매물 소화']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1819000</v>
+        <v>276750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F6" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G6" t="n">
-        <v>1231</v>
+        <v>1976</v>
       </c>
       <c r="H6" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K6" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L6" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M6" t="n">
-        <v>1810000</v>
+        <v>275000</v>
       </c>
       <c r="N6" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O6" t="n">
-        <v>944760577500</v>
+        <v>829301964750</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R6" t="n">
-        <v>-120000</v>
+        <v>-338000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 증시 신고가 및 엔비디아 강세에 따른 SK하이닉스의 상승 기대감이 있으나, 단기 하락 전망도 존재. 메모리 반도체 업황 개선에 대한 언급.</t>
+          <t>반도체 시장 랠리에 따른 30만 돌파 기대감. 일부 뉴스와 개인적 전망에 기반함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['엔비디아', '반도체', 'AI']</t>
+          <t>['반도체', '영업이익', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1015,6 +1015,98 @@
         </is>
       </c>
       <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1806000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-1.90%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>469</v>
+      </c>
+      <c r="F7" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1335</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1804000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1078262428000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>미국 증시 신고가 및 AI 열풍 속 반도체 섹터 기대감. SK하이닉스 ADR 양전 및 프리장 강세.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['AI 열풍', 'ADR', '반도체 섹터']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
